--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="815">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250721120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2155,12 +2155,6 @@
     <t>Préparateur en pharmacie (officine)</t>
   </si>
   <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>Auxiliaire de vie sociale</t>
-  </si>
-  <si>
     <t>319</t>
   </si>
   <si>
@@ -2183,12 +2177,6 @@
   </si>
   <si>
     <t>Assistant familial</t>
-  </si>
-  <si>
-    <t>323</t>
-  </si>
-  <si>
-    <t>Aide médico-psychologique (AMP)</t>
   </si>
   <si>
     <t>324</t>
@@ -5455,7 +5443,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -6024,34 +6012,18 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>814</v>
+        <v>42</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>815</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>816</v>
+        <v>43</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>818</v>
+        <v>814</v>
       </c>
     </row>
   </sheetData>
